--- a/src/Layers/W1/BaseApp/Inventory/Reports/ItemAgeCompositionValue.xlsx
+++ b/src/Layers/W1/BaseApp/Inventory/Reports/ItemAgeCompositionValue.xlsx
@@ -24,15 +24,16 @@
     <sheet name="Aggregated Metadata" sheetId="4" state="hidden" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="EndingDateFilter" localSheetId="1">_xlfn.XLOOKUP("PeriodStartDate[5]", ReportRequestPageValues[Request Page Option], ReportRequestPageValues[Request Page Option Value])</definedName>
-    <definedName name="EndingDateFilter">_xlfn.XLOOKUP("PeriodStartDate[5]", ReportRequestPageValues[Request Page Option], ReportRequestPageValues[Request Page Option Value])</definedName>
+    <definedName name="EndingDateFilter" localSheetId="1">IFERROR(INDEX(Data[EndingDateText],1)&amp;"","")</definedName>
+    <definedName name="EndingDateFilter">IFERROR(INDEX(Data[EndingDateText],1)&amp;"","")</definedName>
     <definedName name="ExternalData_1" localSheetId="4" hidden="1">ItemAgeComposValue_Query!$A$1:$Q$2</definedName>
-    <definedName name="Period1Text" localSheetId="1">_xlfn.XLOOKUP("Period1Text", ReportRequestPageValues[Request Page Option], ReportRequestPageValues[Request Page Option Value])</definedName>
-    <definedName name="Period1Text">_xlfn.XLOOKUP("Period1Text", ReportRequestPageValues[Request Page Option], ReportRequestPageValues[Request Page Option Value])</definedName>
-    <definedName name="Period2Text" localSheetId="1">_xlfn.XLOOKUP("Period2Text", ReportRequestPageValues[Request Page Option], ReportRequestPageValues[Request Page Option Value])</definedName>
-    <definedName name="Period2Text">_xlfn.XLOOKUP("Period2Text", ReportRequestPageValues[Request Page Option], ReportRequestPageValues[Request Page Option Value])</definedName>
-    <definedName name="Period3Text" localSheetId="1">_xlfn.XLOOKUP("Period3Text", ReportRequestPageValues[Request Page Option], ReportRequestPageValues[Request Page Option Value])</definedName>
-    <definedName name="Period3Text">_xlfn.XLOOKUP("Period3Text", ReportRequestPageValues[Request Page Option], ReportRequestPageValues[Request Page Option Value])</definedName>
+    <definedName name="LocationFilter">IFERROR(INDEX(Data[LocationFilterText],1)&amp;"","")</definedName>
+    <definedName name="Period1Text" localSheetId="1">IFERROR(INDEX(Data[Period1RangeText],1)&amp;"","")</definedName>
+    <definedName name="Period1Text">IFERROR(INDEX(Data[Period1RangeText],1)&amp;"","")</definedName>
+    <definedName name="Period2Text" localSheetId="1">IFERROR(INDEX(Data[Period2RangeText],1)&amp;"","")</definedName>
+    <definedName name="Period2Text">IFERROR(INDEX(Data[Period2RangeText],1)&amp;"","")</definedName>
+    <definedName name="Period3Text" localSheetId="1">IFERROR(INDEX(Data[Period3RangeText],1)&amp;"","")</definedName>
+    <definedName name="Period3Text">IFERROR(INDEX(Data[Period3RangeText],1)&amp;"","")</definedName>
     <definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="1">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
     <definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet" localSheetId="2">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
     <definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
@@ -177,7 +178,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="114">
   <si>
     <t>Language</t>
   </si>
@@ -504,6 +505,21 @@
   </si>
   <si>
     <t>$InvAfterLbl$</t>
+  </si>
+  <si>
+    <t>EndingDateText</t>
+  </si>
+  <si>
+    <t>Period1RangeText</t>
+  </si>
+  <si>
+    <t>Period2RangeText</t>
+  </si>
+  <si>
+    <t>Period3RangeText</t>
+  </si>
+  <si>
+    <t>LocationFilterText</t>
   </si>
 </sst>
 </file>
@@ -2830,9 +2846,9 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}" name="Data" displayName="Data" ref="A1:Q2" totalsRowShown="0" headerRowDxfId="23">
-  <autoFilter ref="A1:Q2" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}"/>
-  <tableColumns count="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}" name="Data" displayName="Data" ref="A1:V2" totalsRowShown="0" headerRowDxfId="23">
+  <autoFilter ref="A1:V2" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}"/>
+  <tableColumns count="22">
     <tableColumn id="11" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="PrintLine"/>
     <tableColumn id="32" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="TotalInvtValue_ItemLedgEntry"/>
     <tableColumn id="33" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="InvtValue5_ItemLedgEntry"/>
@@ -2850,6 +2866,11 @@
     <tableColumn id="39" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="No_Item"/>
     <tableColumn id="40" xr3:uid="{C81517BC-B460-403F-86E0-990D7DAA80E8}" name="InventoryPostingGroup_Item"/>
     <tableColumn id="41" xr3:uid="{4B19C94C-5AE0-456E-B216-C3DDADD34028}" name="StatisticsGroup_Item"/>
+    <tableColumn id="42" xr3:uid="{1D6EC04F-361F-44FC-9978-0883E51746B5}" name="EndingDateText"/>
+    <tableColumn id="43" xr3:uid="{FF87C6D8-BD5F-4A29-B191-A044CDF4113E}" name="Period1RangeText"/>
+    <tableColumn id="44" xr3:uid="{EEDA43B9-DBCA-42C0-B501-584DD04C42DC}" name="Period2RangeText"/>
+    <tableColumn id="45" xr3:uid="{3D347558-2A58-44E5-A40F-B91036AD7E9F}" name="Period3RangeText"/>
+    <tableColumn id="46" xr3:uid="{8365E80A-EFB7-4ED3-80EF-065ADA21628D}" name="LocationFilterText"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3171,6 +3192,14 @@
       </c>
     </row>
     <row r="5" spans="2:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="10" t="str">
+        <f>IF(LocationFilter="","",Caption.LocationFilterLbl)</f>
+        <v/>
+      </c>
+      <c r="C5" s="15" t="str">
+        <f>LocationFilter</f>
+        <v/>
+      </c>
       <c r="I5" s="5"/>
     </row>
     <row r="6" spans="2:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3299,6 +3328,14 @@
       </c>
     </row>
     <row r="5" spans="2:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="10" t="str">
+        <f>IF(LocationFilter="","",Caption.LocationFilterLbl)</f>
+        <v/>
+      </c>
+      <c r="C5" s="15" t="str">
+        <f>LocationFilter</f>
+        <v/>
+      </c>
       <c r="I5" s="5"/>
     </row>
     <row r="6" spans="2:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3704,7 +3741,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
@@ -3713,7 +3750,7 @@
     <col min="27" max="27" width="8.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>64</v>
       </c>
@@ -3765,8 +3802,23 @@
       <c r="Q1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R1" t="s">
+        <v>109</v>
+      </c>
+      <c r="S1" t="s">
+        <v>110</v>
+      </c>
+      <c r="T1" t="s">
+        <v>111</v>
+      </c>
+      <c r="U1" t="s">
+        <v>112</v>
+      </c>
+      <c r="V1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>74</v>
       </c>
